--- a/appendix/01_sliding windows with time series.xlsx
+++ b/appendix/01_sliding windows with time series.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\조근하\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A12D69B6-71FC-4695-965A-DF3F1C74CF33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3B820FA-4D27-49FB-AE55-A6DE2E6A027D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="32">
   <si>
     <r>
       <t>9</t>
@@ -1731,6 +1731,156 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>215153</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>89648</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>887506</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>134471</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그래픽 2" descr="조금 굽은 화살표">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EDDA894C-DC0C-0242-6EDF-C6BC9A106324}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2707341" y="8704730"/>
+          <a:ext cx="672353" cy="672353"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>116541</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>277906</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>788894</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>8965</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="그래픽 3" descr="조금 굽은 화살표">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCE0D1CC-B7E2-4B28-98F8-6903CB4C94C8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3630706" y="15482047"/>
+          <a:ext cx="672353" cy="672353"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>179293</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>233083</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>851646</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>277907</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="그래픽 5" descr="조금 굽은 화살표">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7EA6963-633F-452C-9BAA-EDE9351C38D5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2671481" y="21398754"/>
+          <a:ext cx="672353" cy="672353"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1997,7 +2147,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P78"/>
+  <dimension ref="A1:P88"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="24.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9.59765625" style="1" bestFit="1" customWidth="1"/>
@@ -2007,7 +2157,8 @@
     <col min="6" max="6" width="11.5" style="1" customWidth="1"/>
     <col min="7" max="7" width="12" style="1" customWidth="1"/>
     <col min="8" max="9" width="11.8984375" style="1" customWidth="1"/>
-    <col min="10" max="12" width="14.59765625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10" style="1" customWidth="1"/>
+    <col min="11" max="12" width="14.59765625" style="1" customWidth="1"/>
     <col min="13" max="15" width="9.8984375" style="1" customWidth="1"/>
     <col min="16" max="16384" width="9" style="1"/>
   </cols>
@@ -3421,9 +3572,7 @@
       <c r="F77" s="21">
         <v>19.2</v>
       </c>
-      <c r="G77" s="22" t="s">
-        <v>14</v>
-      </c>
+      <c r="G77" s="22"/>
     </row>
     <row r="78" spans="2:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B78" s="4">
@@ -3441,6 +3590,12 @@
       </c>
       <c r="G78" s="22" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="88" spans="8:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="H88" s="1">
+        <f>120/24</f>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
